--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI2"/>
+  <dimension ref="A1:CI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>263.992</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.06</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,288 +1009,4598 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>55.12</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>56.86</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>59.28</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-28.39</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-113.48</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>29982893.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>27325142.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>70871687.6</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2657750</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-4799229.377777515</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-2145262.02</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>54.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>859.439</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-3.95</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>55.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>57.07</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>59.42</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-20.32</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-112.52</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>30810714.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>28427276.6</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>71965384.46</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>2383438</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-5281768.897985027</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1598621.31</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>952.128</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-10.08</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>56.22000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>57.31</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>59.56</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>59.23</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-8.99</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-111.89</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>25992585.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>25254632.5</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>72823093.42</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>737953</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-5951432.094936458</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-3313920.55</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-5.31</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>281.766</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-6.19</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-9.90</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-7.97</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-3.61</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>56.66</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>57.52</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>59.68</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-111.62</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>20762488.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>23044675.4</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>73396602.94</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-2282186</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-6430979.648412267</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-6293886.05</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-3.08</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>196.879</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-5.82</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-13.59</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-8.29</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-3.72</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>56.88</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>57.57</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>59.79</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-111.56</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>11143003.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>21951634.2</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>25405032.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>75419606.76</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-3453398</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-6455905.757767605</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-6375046.04</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>485.041</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-5.63</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-9.51</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-8.46</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>23.08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>57.72</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>59.92</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>59.23</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-4.50</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-111.42</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>27154672.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>24667392.2</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>27258318.2</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>79188309.68</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-2590926</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-6470607.524677305</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-5741199.81</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>401.833</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-6.02</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-8.13</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>49.27</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>57.38</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>57.97</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>60.04</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>59.22</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-111.30</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>22755797.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>26043838.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>27711987.6</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>85688285.96</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-1668149</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-6603227.108476495</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-6346198.32</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>464.395</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-7.88</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-32.37</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-6.50</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>69.23</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>58.24</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>57.54</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-111.26</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>26742952.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>24516679.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>36252527.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>89433496.94</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-11735848</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-6649959.615648801</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-6512523.92</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>382.341</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-37.15</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-6.18</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>78.57</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>51.83</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>58.42</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-111.36</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>21961747.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>25326862.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>40297305.9</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>89685508.6</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-14970443</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-6674947.923535203</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-6944736.97</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>56.1</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>429.27</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-30.09</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-6.83</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>26.92</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>8.97</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>57.12</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>58.88</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>60.19</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>59.19</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-24.21</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>34.62</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-2.69</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>57.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>58.55</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>59.18</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-7.33</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-110.81</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>340708181.0159091</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>15120001.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>29380136.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>42619865.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>90864066.74</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-13239729</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-6583586.088250012</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-7195021.75</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-111.35</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>24721793.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>28858431.2</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>41279456.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>89986915.22</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-12421025</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-6625895.370469017</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-6801885.89</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>-1.88</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.421423718361266</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>9.706318657345912</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>7.884764051476033</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>2.69</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>585.383</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-8.63</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-29.49</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-5.85</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>25.64</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>57.16</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-11.72</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-111.14</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>34036904.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>29849244.2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>42331695.0</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>90805826.98</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-12482450</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-6593897.095029591</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-6650607.63</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,59 +2322,59 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,57 +2733,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,64 +3610,64 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,72 +4026,72 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-10.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>429.27</t>
+          <t>382.341</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-37.15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,52 +4888,52 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.17999999999999</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.55</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4943,17 +4943,17 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-111.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24721793.0</t>
+          <t>21961747.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>28858431.2</t>
+          <t>25326862.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>41279456.2</t>
+          <t>40297305.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>89986915.22</t>
+          <t>89685508.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-12421025</t>
+          <t>-14970443</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6625895.370469017</t>
+          <t>-6674947.923535203</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-6801885.89</v>
+        <v>-6944736.97</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>585.383</t>
+          <t>429.27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-10.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,52 +5319,52 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>57.17999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.55</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,22 +5374,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.18</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.14</t>
+          <t>-111.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34036904.0</t>
+          <t>24721793.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29849244.2</t>
+          <t>28858431.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>42331695.0</t>
+          <t>41279456.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>90805826.98</t>
+          <t>89986915.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-12482450</t>
+          <t>-12421025</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6593897.095029591</t>
+          <t>-6625895.370469017</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6650607.63</v>
+        <v>-6801885.89</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1044878.26</v>
+        <v>-1885548.44</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,59 +2753,59 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,57 +3164,57 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,64 +4041,64 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.79</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,72 +4457,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>429.27</t>
+          <t>382.341</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.4</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-37.15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,52 +5319,52 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.17999999999999</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.55</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-111.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>24721793.0</t>
+          <t>21961747.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28858431.2</t>
+          <t>25326862.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41279456.2</t>
+          <t>40297305.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>89986915.22</t>
+          <t>89685508.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-12421025</t>
+          <t>-14970443</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6625895.370469017</t>
+          <t>-6674947.923535203</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6801885.89</v>
+        <v>-6944736.97</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1885548.44</v>
+        <v>-3089720.84</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-1044878.26</v>
+        <v>-1885548.44</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,42 +2317,42 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,59 +3184,59 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,52 +3600,52 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,64 +4472,64 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,67 +4893,67 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-3089720.84</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3695793.352504438</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-3434013.020100649</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>17027345</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-10.10</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-12.16</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>51.3</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-1885548.44</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3743389.776577854</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-3089720.839649871</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>11408872</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-11.47</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>-10.10</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-1044878.26</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3862238.674201123</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1885548.444732688</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>20246765</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-11.13</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-11.47</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-2145262.02</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4221636.897740839</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1044878.257539123</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>42074242</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-11.13</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,42 +2773,42 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-1598621.31</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4799229.377777515</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-2145262.016636197</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>23015566</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-7.53</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-3313920.55</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-5281768.897985027</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-1598621.314752154</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>46846442</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-5.31</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>56.6</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,59 +3650,59 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,175 +3720,175 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-6293886.05</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-5951432.094936458</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-3313920.550819516</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>52893437</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-3.08</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-5.31</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,20 +3898,25 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,57 +4066,57 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4086,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-6375046.04</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6430979.648412267</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-6293886.04695791</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>16016019</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-3.08</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>56.8</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-5741199.81</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6455905.757767605</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-6375046.039764259</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>11143003</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-3.60</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,64 +4953,64 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-6346198.32</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6470607.524677305</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-5741199.813781753</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>27154672</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,72 +5374,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>331</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>334479119.8620178</t>
+          <t>334021433.7844445</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-6512523.92</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-6603227.108476495</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-6346198.319028817</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>22755797</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-1.54</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>5.07</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>16.51</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>28.38</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>58.3</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,42 +3209,42 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,59 +4086,59 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,57 +4502,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-5741199.813781753</t>
+          <t>-6375046.039764259</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>27154672</v>
+        <v>11143003</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,64 +5389,64 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6346198.319028817</t>
+          <t>-5741199.813781753</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>22755797</v>
+        <v>27154672</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>274.793</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>307.156</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21316600.4</t>
+          <t>15743790.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>67714501.66</t>
+          <t>65312254.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>15825778</v>
+        <v>14210191</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,42 +3645,42 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,59 +4522,59 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,57 +4938,57 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4998,17 +4998,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-5741199.813781753</t>
+          <t>-6375046.039764259</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>27154672</v>
+        <v>11143003</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>55.01</t>
+          <t>54.78</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>15743790.2</t>
+          <t>14968564.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>65312254.98</t>
+          <t>55328963.9</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>14210191</v>
+        <v>16370637</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,37 +1455,37 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1495,32 +1495,32 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21316600.4</t>
+          <t>15743790.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>67714501.66</t>
+          <t>65312254.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>15825778</v>
+        <v>14210191</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,127 +2627,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>217.689</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>-0.38</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>392.184</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-14.63</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.39</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-4.66</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>28.13</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-15.93</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,42 +4081,42 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4958,59 +4958,59 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,52 +5379,52 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5434,17 +5434,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>54.78</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>58.02</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>16370637.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>14968564.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>14968564.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>25991927.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>55328963.9</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>55328963.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-3761738.343921479</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>16370637</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>16370637.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>14210191.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>15743790.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>15743790.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>25956465.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>65312254.98</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>65312254.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-3880161.860334959</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>14210191</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>14210191.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>55.27</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>15825778.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>21316600.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>21316600.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>25649746.9</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>67714501.66</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>67714501.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3679284.745913677</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>15825778</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>15825778.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>52.14</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>17027345.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>22754558.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>22754558</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>26782636.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>69191727.6</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>69191727.59999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-3434013.020100649</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>17027345</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>17027345.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>58.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>11408872.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>28718377.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>28718377.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>27355481.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>69373581.34</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>69373581.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-3089720.839649871</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>11408872</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>11408872.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>58.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>20246765.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>37015290.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>37015290.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>28888889.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>69945836.02</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>69945836.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1885548.444732688</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>20246765</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>20246765.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>54.21999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>59.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>42074242.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>36169141.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>36169141.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>29060387.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>70323701.58</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>70323701.58</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-1044878.257539123</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>42074242</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>42074242.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>55.12</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>23015566.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>29982893.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>29982893.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>27325142.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>70871687.6</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>70871687.59999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2145262.016636197</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>23015566</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>57.07</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>59.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>46846442.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>30810714.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>30810714.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>28427276.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>71965384.46</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>71965384.45999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-1598621.314752154</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>46846442</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>52893437.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>25992585.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>25992585.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>25254632.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>72823093.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>72823093.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-3313920.550819516</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>52893437</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>16016019.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>20762488.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>20762488.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>23044675.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>73396602.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>73396602.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-6293886.04695791</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>16016019</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN3" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,42 +1874,42 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN4" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN9" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,39 +4469,39 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>57.31</v>
+        <v>57.07</v>
       </c>
       <c r="AN11" t="n">
-        <v>59.56</v>
+        <v>59.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>25992585.6</v>
+        <v>30810714.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>72823093.42</v>
+        <v>71965384.45999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,55 +5334,55 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>57.52</v>
+        <v>57.31</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.68</v>
+        <v>59.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>20762488.6</v>
+        <v>25992585.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>73396602.94</v>
+        <v>72823093.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN4" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,42 +2304,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2348,29 +2348,29 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN10" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN11" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>57.31</v>
+        <v>57.07</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.56</v>
+        <v>59.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>25992585.6</v>
+        <v>30810714.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>72823093.42</v>
+        <v>71965384.45999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-23.55</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-14.63</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>0.57</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-31.01</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-15.12</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-1.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN4" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,42 +2734,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,29 +2778,29 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN6" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3416,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN11" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3208,29 +3208,29 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,42 +1014,42 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,68 +2304,68 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN6" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,42 +3594,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3638,29 +3638,29 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,42 +4753,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>217.689</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>-0.38</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>392.184</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>219.546</t>
+          <t>243.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,42 +1444,42 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN7" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,42 +4024,42 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4068,29 +4068,29 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>638</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>330348525.830161</t>
+          <t>329940052.1820176</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.47</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>2453</t>
@@ -883,12 +879,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +894,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +909,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +979,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1010,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1032,56 +1028,48 @@
           <t>92.31</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
+      <c r="AH2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.85</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>14.29</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
+          <t>19.27</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.46</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1078,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1088,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1144,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1189,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1199,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1214,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1229,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1254,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1289,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>2453</t>
@@ -1313,12 +1297,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1312,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1322,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1397,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1407,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,17 +1428,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1462,56 +1446,48 @@
           <t>92.31</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
+      <c r="AH3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1.42</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>10.30</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.43</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
+          <t>14.29</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.53</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1496,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1506,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1562,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1607,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1617,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1632,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1647,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1672,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1687,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1707,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>2453</t>
@@ -1743,12 +1715,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>219.546</t>
+          <t>243.53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1730,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1740,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1815,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1825,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,42 +1846,38 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
+          <t>92.31</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.07</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1918,30 +1886,26 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>8.31</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
+          <t>10.30</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.59</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1914,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1924,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1980,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,12 +2035,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2050,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2065,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2090,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2100,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2125,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>2453</t>
@@ -2173,12 +2133,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2158,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2243,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2264,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,59 +2279,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.67</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-3.25</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-2.56</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4.34</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
+          <t>8.31</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.63</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2332,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2342,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2443,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2458,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2468,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2483,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2508,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2591,11 +2543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>2453</t>
@@ -2603,12 +2551,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2566,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2576,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2651,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2661,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2682,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,59 +2697,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60.68</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
+          <t>81.67</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-3.25</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
+          <t>4.34</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1.66</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2750,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2760,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2816,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2861,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2876,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2886,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2901,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2926,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2973,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2988,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +2998,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3073,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,7 +3083,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3153,7 +3093,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3104,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>32.35</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-5.06</t>
-        </is>
+          <t>60.68</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-4.2</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.38</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.68</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3172,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3182,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3238,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3283,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3293,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3308,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3323,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3348,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3395,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3410,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3420,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3495,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3505,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3526,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.35</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-5.33</t>
-        </is>
+          <t>32.35</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-5.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN8" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.93</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.65</t>
-        </is>
+          <t>-6.38</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.68</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3594,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3604,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3660,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3705,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3715,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3730,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3745,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3770,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3817,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3832,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3842,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3917,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3927,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3948,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-5.94</t>
-        </is>
+          <t>17.35</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-5.33</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.37</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.60</t>
-        </is>
+          <t>-11.93</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.65</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4016,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4026,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4082,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4127,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4137,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4152,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4167,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4192,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4239,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4254,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4264,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4339,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4349,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,42 +4370,38 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.44</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-6.39</t>
-        </is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-5.94</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4498,30 +4410,26 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-26.31</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-1.93</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
+          <t>-19.37</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.6</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4438,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4448,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4504,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4549,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4559,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4574,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4589,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4614,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4661,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4686,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4863,17 +4771,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4792,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4902,56 +4810,48 @@
           <t>5.44</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.61</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-6.21</t>
-        </is>
+      <c r="AH11" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-6.39</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-30.14</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.43</t>
-        </is>
+          <t>-26.31</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.53</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4860,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4870,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5086,7 +4986,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +4996,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5011,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5036,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,12 +5083,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5098,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5108,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5183,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5193,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5214,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>183</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5232,48 @@
           <t>5.44</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-6.21</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-31.69</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.74</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.32</t>
-        </is>
+          <t>-30.14</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.43</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5282,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5292,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>329940052.1820176</t>
+          <t>329479527.4291971</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5348,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5393,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5403,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5418,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5433,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5458,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>2453</t>
@@ -879,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -894,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -909,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -979,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -989,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1015,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1088,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1189,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1199,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1214,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1229,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1254,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1289,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2453</t>
@@ -1297,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1312,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1322,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1407,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1433,7 +1441,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1447,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1506,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1562,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1607,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1617,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1632,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1647,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1672,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1707,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2453</t>
@@ -1715,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1730,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1740,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1815,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1825,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1851,12 +1863,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1865,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AI4" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1914,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1924,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2025,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2035,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2050,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2065,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2090,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2105,7 +2117,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2125,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2453</t>
@@ -2133,42 +2149,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2233,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2243,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2269,33 +2285,33 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2304,26 +2320,26 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2332,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2342,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2398,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2453,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2468,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2483,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2508,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2518,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2543,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2453</t>
@@ -2551,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2576,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2661,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2687,7 +2707,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2697,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3.25</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.59</v>
+        <v>-1.49</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2750,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2760,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2861,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2876,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2886,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2901,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2926,12 +2946,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -2963,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2973,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2988,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2998,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3073,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3083,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3109,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3119,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="AI7" t="n">
-        <v>-4.2</v>
+        <v>-3.25</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.68</v>
+        <v>-1.66</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3172,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3182,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3238,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3298,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3308,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3323,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3348,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3395,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3410,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3420,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3495,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3505,7 +3525,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3515,7 +3535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3531,58 +3551,58 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.06</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.79</v>
+        <v>-1.69</v>
       </c>
       <c r="AR8" t="n">
         <v>-1.68</v>
@@ -3594,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3604,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3660,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3715,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3730,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3745,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3770,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3817,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3832,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3842,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3917,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3927,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3953,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.33</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.85</v>
+        <v>-1.79</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.65</v>
+        <v>-1.68</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4016,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4026,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4082,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4137,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4152,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4167,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4192,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4239,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4254,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4264,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4339,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4349,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4375,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.94</v>
+        <v>-5.33</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.91</v>
+        <v>-1.85</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.6</v>
+        <v>-1.65</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4438,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4448,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4504,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4559,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4574,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4589,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4614,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4661,42 +4681,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>274.793</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>307.156</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.57</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4761,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4771,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4797,33 +4817,33 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.85</v>
+        <v>0.31</v>
       </c>
       <c r="AI11" t="n">
-        <v>-6.39</v>
+        <v>-5.94</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4832,26 +4852,26 @@
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.93</v>
+        <v>-1.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.53</v>
+        <v>-1.6</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4860,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4870,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4926,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4981,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -4996,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5011,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5036,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5083,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5108,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5193,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5219,7 +5239,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5233,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.61</v>
+        <v>-0.85</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.21</v>
+        <v>-6.39</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.85</v>
+        <v>-1.93</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.43</v>
+        <v>-1.53</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5282,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5292,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>329479527.4291971</t>
+          <t>329021965.9198251</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5408,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5418,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5433,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.25</t>
+          <t>28.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5458,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,34 +1305,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>197.456</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>182.616</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>53.2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,42 +2571,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,33 +2707,33 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2742,26 +2742,26 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.25</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.59</v>
+        <v>-1.49</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.2</v>
+        <v>-3.25</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.68</v>
+        <v>-1.66</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,58 +3973,58 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.06</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.79</v>
+        <v>-1.69</v>
       </c>
       <c r="AR9" t="n">
         <v>-1.68</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.33</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN10" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.85</v>
+        <v>-1.79</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.65</v>
+        <v>-1.68</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.94</v>
+        <v>-5.33</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.91</v>
+        <v>-1.85</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.6</v>
+        <v>-1.65</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,42 +5103,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>274.793</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>307.156</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,33 +5239,33 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.85</v>
+        <v>0.31</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.39</v>
+        <v>-5.94</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5274,26 +5274,26 @@
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.93</v>
+        <v>-1.91</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.53</v>
+        <v>-1.6</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>329021965.9198251</t>
+          <t>328589649.6462882</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.23</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>399.383</t>
+          <t>413.751</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>52.85999999999999</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.82</v>
+        <v>52.66</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.38</v>
+        <v>56.23</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.73</t>
+          <t>-116.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>17632111.8</v>
+        <v>19530329.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15437836.6</t>
+          <t>16029526.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>34153376.64</v>
+        <v>34088378.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2194275</t>
+          <t>3500802</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2783108.98340875</t>
+          <t>-2501654.011702673</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1557820.375000447</t>
+          <t>-953651.6673192494</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,17 +1436,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,17 +2702,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,38 +3124,38 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3164,26 +3164,26 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.25</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.59</v>
+        <v>-1.49</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.2</v>
+        <v>-3.25</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.68</v>
+        <v>-1.66</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,63 +4390,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.06</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.79</v>
+        <v>-1.69</v>
       </c>
       <c r="AR10" t="n">
         <v>-1.68</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.33</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN11" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.85</v>
+        <v>-1.79</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.65</v>
+        <v>-1.68</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.31</v>
+        <v>0.85</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.94</v>
+        <v>-5.33</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.91</v>
+        <v>-1.85</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.6</v>
+        <v>-1.65</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>328589649.6462882</t>
+          <t>328160640.4229651</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>413.751</t>
+          <t>246.617</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.75</v>
+        <v>-0.41</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.11999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>52.66</v>
+        <v>52.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>56.23</v>
+        <v>56.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.22</v>
+        <v>-1.14</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.52</t>
+          <t>-115.39</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>19530329.2</v>
+        <v>15349501.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>16029526.5</t>
+          <t>16117290.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>34088378.66</v>
+        <v>32724534.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3500802</t>
+          <t>-767789</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2501654.011702673</t>
+          <t>-2301190.37609602</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-953651.6673192494</t>
+          <t>-1198640.380259432</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>399.383</t>
+          <t>413.751</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>52.85999999999999</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>52.82</v>
+        <v>52.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.38</v>
+        <v>56.23</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.73</t>
+          <t>-116.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>17632111.8</v>
+        <v>19530329.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15437836.6</t>
+          <t>16029526.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>34153376.64</v>
+        <v>34088378.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2194275</t>
+          <t>3500802</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2783108.98340875</t>
+          <t>-2501654.011702673</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1557820.375000447</t>
+          <t>-953651.6673192494</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,17 +1858,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,17 +3124,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,42 +3415,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,38 +3546,38 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.25</v>
+        <v>-2.56</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.59</v>
+        <v>-1.49</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,34 +4259,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>270.323</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>225.533</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.2</v>
+        <v>-3.25</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN10" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.68</v>
+        <v>-1.66</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,63 +4812,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.06</v>
+        <v>-4.2</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.79</v>
+        <v>-1.69</v>
       </c>
       <c r="AR11" t="n">
         <v>-1.68</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.33</v>
+        <v>-5.06</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN12" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.85</v>
+        <v>-1.79</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.65</v>
+        <v>-1.68</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>328160640.4229651</t>
+          <t>327712796.7387518</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>166.594</t>
+          <t>129.578</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1099,61 +1099,61 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>52.5</v>
+        <v>52.48</v>
       </c>
       <c r="AV2" t="n">
-        <v>55.86</v>
+        <v>55.69</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>57.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.72</v>
+        <v>-0.67</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1.05</v>
+        <v>-0.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-113.24</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>15192941.8</v>
+        <v>14493492.4</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>15823633.9</t>
+          <t>15085603.2</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>31861063.22</v>
+        <v>31088486.92</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-630692</t>
+          <t>-592110</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-2201724.717436798</t>
+          <t>-2183076.323235282</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-1654663.594811073</t>
+          <t>-2080510.155126946</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>246.617</t>
+          <t>166.594</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.98</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1561,61 +1561,61 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-0.41</v>
+        <v>0.15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>53.11999999999999</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>52.54</v>
+        <v>52.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>56.04</v>
+        <v>55.86</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.8</v>
+        <v>-0.72</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-115.39</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>15349501.4</v>
+        <v>15192941.8</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>16117290.7</t>
+          <t>15823633.9</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>32724534.4</v>
+        <v>31861063.22</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-767789</t>
+          <t>-630692</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-2301190.37609602</t>
+          <t>-2201724.717436798</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-1198640.380259432</t>
+          <t>-1654663.594811073</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>413.751</t>
+          <t>246.617</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2023,61 +2023,61 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.75</v>
+        <v>-0.41</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.11999999999999</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>52.66</v>
+        <v>52.54</v>
       </c>
       <c r="AV4" t="n">
-        <v>56.23</v>
+        <v>56.04</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1.22</v>
+        <v>-1.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-116.52</t>
+          <t>-115.39</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>19530329.2</v>
+        <v>15349501.4</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>16029526.5</t>
+          <t>16117290.7</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>34088378.66</v>
+        <v>32724534.4</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3500802</t>
+          <t>-767789</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-2501654.011702673</t>
+          <t>-2301190.37609602</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-953651.6673192494</t>
+          <t>-1198640.380259432</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>399.383</t>
+          <t>413.751</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>-0.94</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2499,47 +2499,47 @@
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>52.85999999999999</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>52.82</v>
+        <v>52.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>56.38</v>
+        <v>56.23</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-117.73</t>
+          <t>-116.52</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>17632111.8</v>
+        <v>19530329.2</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>15437836.6</t>
+          <t>16029526.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>34153376.64</v>
+        <v>34088378.66</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2194275</t>
+          <t>3500802</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-2783108.98340875</t>
+          <t>-2501654.011702673</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-1557820.375000447</t>
+          <t>-953651.6673192494</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2961,47 +2961,47 @@
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AV6" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3409,61 +3409,61 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AV7" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -3885,47 +3885,47 @@
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AV8" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4347,47 +4347,47 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AV9" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,42 +4619,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4795,33 +4795,33 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -4830,26 +4830,26 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AV10" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5267,51 +5267,51 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.25</v>
+        <v>-2.56</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AV11" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-1.59</v>
+        <v>-1.49</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5729,51 +5729,51 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.88</v>
+        <v>0.57</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-4.2</v>
+        <v>-3.25</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AV12" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-1.69</v>
+        <v>-1.59</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.68</v>
+        <v>-1.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>327257135.2934783</t>
+          <t>326798509.1374819</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.16</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-0.37</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>58.33</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>61.11</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>1.29</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-5.76</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-3.55</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>53.16</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>52.48</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>55.69</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>57.74</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>31.38</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.67</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.98</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-113.24</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>6897641.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>14493492.4</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>15085603.2</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>31088486.92</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-592110</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-2183076.323235282</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-2080510.155126946</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>6897641.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-9.25</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>2.49</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-0.18</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0.15</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>1.18</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-6.02</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-3.37</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>53.12</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>52.5</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>55.86</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>57.81</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>31.26</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-1.05</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-114.28</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>8870933.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>15192941.8</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>15823633.9</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>31861063.22</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-630692</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-2201724.717436798</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-1654663.594811073</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>8870933.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-8.90</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>53.6</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>53.2</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-0.37</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.41</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>1.1</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-6.25</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-3.18</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>53.11999999999999</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>52.54</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>56.04</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>57.89</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>29.32</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-1.14</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-115.39</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>13064228.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>15349501.4</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>16117290.7</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>32724534.4</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-767789</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-2301190.37609602</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-1198640.380259432</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>13064228.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-9.42</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>2.49</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>53.5</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>53.5</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>52.9</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.31</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>86.67</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.75</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>0.84</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-6.34</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-2.98</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>52.66</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>56.23</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>57.95</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>29.38</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.86</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-1.22</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-116.52</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>22287536.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>19530329.2</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>16029526.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>34088378.66</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>3500802</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-2501654.011702673</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-953651.6673192494</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>22287536.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-8.39</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>54.2</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>54.3</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>53.4</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>53.5</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.94</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>86.67</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.64</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>0.09</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-6.32</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.83</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>52.85999999999999</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>52.82</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>56.38</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>58.02</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>24.83</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.98</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-1.31</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-117.73</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>21347124.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>17632111.8</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>15437836.6</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>34153376.64</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>2194275</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-2783108.98340875</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-1557820.375000447</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>21347124.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-8.90</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>53.2</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>53.8</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>53.2</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.20</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>86.67</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>0.11</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-0.44</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-6.29</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.67</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>52.73999999999999</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>52.98</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>56.53</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>58.08</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>21.18</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-1.1</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-1.39</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-118.84</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>10394888.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>15677714</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>14724143.3</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>34602869.3</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>953570</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-3005888.730392078</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-2264523.658294994</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>10394888.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-9.59</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>2.48</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>52.4</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>92.31</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>0.95</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-0.85</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-6.26</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.50</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>53.15</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>56.7</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>58.15</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>19.27</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-1.18</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-1.46</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-119.83</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>9653731.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>16454326</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>15267232.3</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>35965380.56</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1187093</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-3140682.379864275</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-2019770.07520524</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>9653731.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-8.90</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>2.50</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>53.5</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>53.2</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-1.88</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>92.31</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.46</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-1.42</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-6.24</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.35</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>52.56</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>53.32</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>56.86</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>58.23</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>14.29</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-1.31</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-1.53</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-120.79</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>33968367.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>16885080</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>16004593.7</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>36758773.74</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>880486</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-3344484.617075008</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-1518577.775248263</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>33968367.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-9.59</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>2.48</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>54.3</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>52.3</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>52.8</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-1.34</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>76.92</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>92.31</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-6.13</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.20</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>52.44</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>53.55</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>57.04</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>58.33</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>10.30</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-1.43</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-1.59</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-121.53</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>12796449.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>12528723.8</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>13748644.2</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>37439432.96</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-1219920</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-3676467.679225326</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-3353493.426193714</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>12796449.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-10.45</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>52.3</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>52.3</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.76</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.31</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-2.56</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-6.01</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-2.00</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>52.44</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>53.82</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>57.26</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>58.43</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>8.31</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-1.49</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-1.63</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-122.09</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>11575135.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>13243561.4</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>14493675.8</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>39880117.8</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-1250114</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-3735190.270685619</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-3586614.090894589</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>11575135.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-9.93</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>52.7</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>53.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>57.9</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/05/27</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-1.33</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>81.67</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>0.57</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-3.25</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-5.88</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-1.87</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>52.3</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>54.05</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>57.43</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>58.53</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>4.34</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-1.59</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-1.66</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-122.55</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>326798509.1374819</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>14277948.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>13770572.6</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>17543586.5</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>40909066.6</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-3773013</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-3762204.121556715</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-3660695.180078171</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>14277948.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-9.93</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>27.7</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>5300</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>53.3</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>129.578</t>
+          <t>252.353</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,61 +1139,61 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.3</v>
+        <v>-0.98</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.29</v>
+        <v>0.96</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.02</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>52.48</v>
+        <v>52.52</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55.69</v>
+        <v>55.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>57.74</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.98</v>
+        <v>-0.91</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-113.24</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>14493492.4</v>
+        <v>12860748</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>15085603.2</t>
+          <t>15246429.9</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>31088486.92</v>
+        <v>29156371.74</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-592110</t>
+          <t>-2385681</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2183076.323235282</t>
+          <t>-2132627.33788676</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2080510.155126946</t>
+          <t>-1855157.918469884</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1383,17 +1383,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>52.5</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>166.594</t>
+          <t>129.578</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,61 +1621,61 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>52.5</v>
+        <v>52.48</v>
       </c>
       <c r="AZ3" t="n">
-        <v>55.86</v>
+        <v>55.69</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>57.74</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.72</v>
+        <v>-0.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1.05</v>
+        <v>-0.98</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-113.24</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>15192941.8</v>
+        <v>14493492.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>15823633.9</t>
+          <t>15085603.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>31861063.22</v>
+        <v>31088486.92</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-630692</t>
+          <t>-592110</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2201724.717436798</t>
+          <t>-2183076.323235282</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1654663.594811073</t>
+          <t>-2080510.155126946</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>246.617</t>
+          <t>166.594</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.98</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,61 +2103,61 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.41</v>
+        <v>0.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>53.11999999999999</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>52.54</v>
+        <v>52.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>56.04</v>
+        <v>55.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.8</v>
+        <v>-0.72</v>
       </c>
       <c r="BD4" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-115.39</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>15349501.4</v>
+        <v>15192941.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>16117290.7</t>
+          <t>15823633.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>32724534.4</v>
+        <v>31861063.22</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-767789</t>
+          <t>-630692</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2301190.37609602</t>
+          <t>-2201724.717436798</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1198640.380259432</t>
+          <t>-1654663.594811073</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>413.751</t>
+          <t>246.617</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.75</v>
+        <v>-0.41</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.11999999999999</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>52.66</v>
+        <v>52.54</v>
       </c>
       <c r="AZ5" t="n">
-        <v>56.23</v>
+        <v>56.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.22</v>
+        <v>-1.14</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-116.52</t>
+          <t>-115.39</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>19530329.2</v>
+        <v>15349501.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>16029526.5</t>
+          <t>16117290.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>34088378.66</v>
+        <v>32724534.4</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3500802</t>
+          <t>-767789</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2501654.011702673</t>
+          <t>-2301190.37609602</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-953651.6673192494</t>
+          <t>-1198640.380259432</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>399.383</t>
+          <t>413.751</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3081,47 +3081,47 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>52.85999999999999</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>52.82</v>
+        <v>52.66</v>
       </c>
       <c r="AZ6" t="n">
-        <v>56.38</v>
+        <v>56.23</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-117.73</t>
+          <t>-116.52</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>17632111.8</v>
+        <v>19530329.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>15437836.6</t>
+          <t>16029526.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>34153376.64</v>
+        <v>34088378.66</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2194275</t>
+          <t>3500802</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2783108.98340875</t>
+          <t>-2501654.011702673</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1557820.375000447</t>
+          <t>-953651.6673192494</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3563,47 +3563,47 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AZ7" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,61 +4031,61 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AZ8" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4527,47 +4527,47 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AU9" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AZ9" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,34 +4799,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>637.704</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>243.53</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AU10" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AZ10" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,42 +5281,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,33 +5477,33 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AU11" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -5512,26 +5512,26 @@
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AZ11" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,51 +5969,51 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AU12" t="n">
-        <v>-3.25</v>
+        <v>-2.56</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AZ12" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.59</v>
+        <v>-1.49</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.66</v>
+        <v>-1.63</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>326798509.1374819</t>
+          <t>326354833.6950867</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>252.353</t>
+          <t>265.598</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.98</v>
+        <v>-0.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>53.02</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>52.52</v>
+        <v>52.56</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55.54</v>
+        <v>55.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>57.61</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.91</v>
+        <v>-0.86</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-112.38</t>
+          <t>-111.61</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>13183402.0</t>
+          <t>14156741.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>12860748</v>
+        <v>11234589</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>15246429.9</t>
+          <t>15382459.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>29156371.74</v>
+        <v>28922957.26</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2385681</t>
+          <t>-4147870</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2132627.33788676</t>
+          <t>-2047304.975111595</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1855157.918469884</t>
+          <t>-1578031.979848191</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>13183402.0</t>
+          <t>14156741.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>129.578</t>
+          <t>252.353</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.3</v>
+        <v>-0.98</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.29</v>
+        <v>0.96</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.02</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>52.48</v>
+        <v>52.52</v>
       </c>
       <c r="AZ3" t="n">
-        <v>55.69</v>
+        <v>55.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>57.74</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.98</v>
+        <v>-0.91</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-113.24</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>14493492.4</v>
+        <v>12860748</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>15085603.2</t>
+          <t>15246429.9</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>31088486.92</v>
+        <v>29156371.74</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-592110</t>
+          <t>-2385681</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2183076.323235282</t>
+          <t>-2132627.33788676</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2080510.155126946</t>
+          <t>-1855157.918469884</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>52.5</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>166.594</t>
+          <t>129.578</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>52.5</v>
+        <v>52.48</v>
       </c>
       <c r="AZ4" t="n">
-        <v>55.86</v>
+        <v>55.69</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>57.74</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.72</v>
+        <v>-0.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>-1.05</v>
+        <v>-0.98</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-113.24</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>15192941.8</v>
+        <v>14493492.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>15823633.9</t>
+          <t>15085603.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>31861063.22</v>
+        <v>31088486.92</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-630692</t>
+          <t>-592110</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2201724.717436798</t>
+          <t>-2183076.323235282</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1654663.594811073</t>
+          <t>-2080510.155126946</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>246.617</t>
+          <t>166.594</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.98</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.41</v>
+        <v>0.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>53.11999999999999</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>52.54</v>
+        <v>52.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>56.04</v>
+        <v>55.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.8</v>
+        <v>-0.72</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-115.39</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>15349501.4</v>
+        <v>15192941.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>16117290.7</t>
+          <t>15823633.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>32724534.4</v>
+        <v>31861063.22</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-767789</t>
+          <t>-630692</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2301190.37609602</t>
+          <t>-2201724.717436798</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1198640.380259432</t>
+          <t>-1654663.594811073</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>413.751</t>
+          <t>246.617</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.75</v>
+        <v>-0.41</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.11999999999999</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>52.66</v>
+        <v>52.54</v>
       </c>
       <c r="AZ6" t="n">
-        <v>56.23</v>
+        <v>56.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.22</v>
+        <v>-1.14</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-116.52</t>
+          <t>-115.39</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>19530329.2</v>
+        <v>15349501.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>16029526.5</t>
+          <t>16117290.7</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>34088378.66</v>
+        <v>32724534.4</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3500802</t>
+          <t>-767789</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2501654.011702673</t>
+          <t>-2301190.37609602</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-953651.6673192494</t>
+          <t>-1198640.380259432</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>399.383</t>
+          <t>413.751</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3563,47 +3563,47 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>52.85999999999999</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>52.82</v>
+        <v>52.66</v>
       </c>
       <c r="AZ7" t="n">
-        <v>56.38</v>
+        <v>56.23</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-117.73</t>
+          <t>-116.52</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>17632111.8</v>
+        <v>19530329.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>15437836.6</t>
+          <t>16029526.5</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>34153376.64</v>
+        <v>34088378.66</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2194275</t>
+          <t>3500802</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2783108.98340875</t>
+          <t>-2501654.011702673</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1557820.375000447</t>
+          <t>-953651.6673192494</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AZ8" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AZ9" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,17 +5472,17 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AU11" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AZ11" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,42 +5763,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,38 +5954,38 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>266</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.31</v>
+        <v>-0.27</v>
       </c>
       <c r="AU12" t="n">
-        <v>-2.56</v>
+        <v>-2.07</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -5994,26 +5994,26 @@
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AZ12" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>326354833.6950867</t>
+          <t>325914545.495671</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.57</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>27.83</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>265.598</t>
+          <t>169.583</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-19.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.3</v>
+        <v>-0.99</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>52.86</t>
+          <t>52.72000000000001</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>52.56</v>
+        <v>52.55</v>
       </c>
       <c r="AZ2" t="n">
-        <v>55.38</v>
+        <v>55.19</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>57.61</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.63</v>
+        <v>-0.64</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-111.61</t>
+          <t>-111.02</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>14156741.0</t>
+          <t>8852668.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>11234589</v>
+        <v>10392277</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>15382459.1</t>
+          <t>12870889.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>28922957.26</v>
+        <v>28000317.22</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-4147870</t>
+          <t>-2478612</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2047304.975111595</t>
+          <t>-2000396.286373935</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1578031.979848191</t>
+          <t>-1742398.498316802</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>14156741.0</t>
+          <t>8852668.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>252.353</t>
+          <t>265.598</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.65</t>
+          <t>-26.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-0.98</v>
+        <v>-0.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>53.02</t>
+          <t>52.86</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>52.52</v>
+        <v>52.56</v>
       </c>
       <c r="AZ3" t="n">
-        <v>55.54</v>
+        <v>55.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>57.61</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.66</v>
+        <v>-0.63</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.91</v>
+        <v>-0.86</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-112.38</t>
+          <t>-111.61</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>13183402.0</t>
+          <t>14156741.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>12860748</v>
+        <v>11234589</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>15246429.9</t>
+          <t>15382459.1</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>29156371.74</v>
+        <v>28922957.26</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-2385681</t>
+          <t>-4147870</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2132627.33788676</t>
+          <t>-2047304.975111595</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1855157.918469884</t>
+          <t>-1578031.979848191</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>13183402.0</t>
+          <t>14156741.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>129.578</t>
+          <t>252.353</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.3</v>
+        <v>-0.98</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.29</v>
+        <v>0.96</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>53.16</t>
+          <t>53.02</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>52.48</v>
+        <v>52.52</v>
       </c>
       <c r="AZ4" t="n">
-        <v>55.69</v>
+        <v>55.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>57.74</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.98</v>
+        <v>-0.91</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-113.24</t>
+          <t>-112.38</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>14493492.4</v>
+        <v>12860748</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>15085603.2</t>
+          <t>15246429.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>31088486.92</v>
+        <v>29156371.74</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-592110</t>
+          <t>-2385681</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-2183076.323235282</t>
+          <t>-2132627.33788676</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2080510.155126946</t>
+          <t>-1855157.918469884</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
+          <t>51.7</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>52.5</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>166.594</t>
+          <t>129.578</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.15</v>
+        <v>-0.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>53.12</t>
+          <t>53.16</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>52.5</v>
+        <v>52.48</v>
       </c>
       <c r="AZ5" t="n">
-        <v>55.86</v>
+        <v>55.69</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>57.81</t>
+          <t>57.74</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.72</v>
+        <v>-0.67</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.05</v>
+        <v>-0.98</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-113.24</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>15192941.8</v>
+        <v>14493492.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>15823633.9</t>
+          <t>15085603.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>31861063.22</v>
+        <v>31088486.92</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-630692</t>
+          <t>-592110</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2201724.717436798</t>
+          <t>-2183076.323235282</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1654663.594811073</t>
+          <t>-2080510.155126946</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>8870933.0</t>
+          <t>6897641.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>246.617</t>
+          <t>166.594</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.98</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.41</v>
+        <v>0.15</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>53.11999999999999</t>
+          <t>53.12</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>52.54</v>
+        <v>52.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>56.04</v>
+        <v>55.86</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>57.89</t>
+          <t>57.81</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.8</v>
+        <v>-0.72</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.14</v>
+        <v>-1.05</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-115.39</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>15349501.4</v>
+        <v>15192941.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>16117290.7</t>
+          <t>15823633.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>32724534.4</v>
+        <v>31861063.22</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-767789</t>
+          <t>-630692</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-2301190.37609602</t>
+          <t>-2201724.717436798</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1198640.380259432</t>
+          <t>-1654663.594811073</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>13064228.0</t>
+          <t>8870933.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>413.751</t>
+          <t>246.617</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.75</v>
+        <v>-0.41</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.84</v>
+        <v>1.1</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.11999999999999</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>52.66</v>
+        <v>52.54</v>
       </c>
       <c r="AZ7" t="n">
-        <v>56.23</v>
+        <v>56.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.22</v>
+        <v>-1.14</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-116.52</t>
+          <t>-115.39</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>19530329.2</v>
+        <v>15349501.4</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>16029526.5</t>
+          <t>16117290.7</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>34088378.66</v>
+        <v>32724534.4</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>3500802</t>
+          <t>-767789</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-2501654.011702673</t>
+          <t>-2301190.37609602</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-953651.6673192494</t>
+          <t>-1198640.380259432</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>22287536.0</t>
+          <t>13064228.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>399.383</t>
+          <t>413.751</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>52.85999999999999</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>52.82</v>
+        <v>52.66</v>
       </c>
       <c r="AZ8" t="n">
-        <v>56.38</v>
+        <v>56.23</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>58.02</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-117.73</t>
+          <t>-116.52</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>17632111.8</v>
+        <v>19530329.2</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>15437836.6</t>
+          <t>16029526.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>34153376.64</v>
+        <v>34088378.66</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>2194275</t>
+          <t>3500802</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-2783108.98340875</t>
+          <t>-2501654.011702673</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1557820.375000447</t>
+          <t>-953651.6673192494</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>21347124.0</t>
+          <t>22287536.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>197.456</t>
+          <t>399.383</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,17 +4508,17 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4527,47 +4527,47 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.44</v>
+        <v>0.09</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>52.73999999999999</t>
+          <t>52.85999999999999</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>52.98</v>
+        <v>52.82</v>
       </c>
       <c r="AZ9" t="n">
-        <v>56.53</v>
+        <v>56.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>58.08</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.18</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1.1</v>
+        <v>-0.98</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.39</v>
+        <v>-1.31</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-118.84</t>
+          <t>-117.73</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>15677714</v>
+        <v>17632111.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>14724143.3</t>
+          <t>15437836.6</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>34602869.3</v>
+        <v>34153376.64</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>953570</t>
+          <t>2194275</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3005888.730392078</t>
+          <t>-2783108.98340875</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2264523.658294994</t>
+          <t>-1557820.375000447</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>10394888.0</t>
+          <t>21347124.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>53.1</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>53.1</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>182.616</t>
+          <t>197.456</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.50</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>92.31</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.95</v>
+        <v>0.11</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.85</v>
+        <v>-0.44</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.73999999999999</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>53.15</v>
+        <v>52.98</v>
       </c>
       <c r="AZ10" t="n">
-        <v>56.7</v>
+        <v>56.53</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>58.08</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-119.83</t>
+          <t>-118.84</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>16454326</v>
+        <v>15677714</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>15267232.3</t>
+          <t>14724143.3</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>35965380.56</v>
+        <v>34602869.3</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1187093</t>
+          <t>953570</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3140682.379864275</t>
+          <t>-3005888.730392078</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2019770.07520524</t>
+          <t>-2264523.658294994</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>9653731.0</t>
+          <t>10394888.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>637.704</t>
+          <t>182.616</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-13.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.46</v>
+        <v>0.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.42</v>
+        <v>-0.85</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>52.56</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>53.32</v>
+        <v>53.15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>56.86</v>
+        <v>56.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>58.23</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>19.27</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.31</v>
+        <v>-1.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.53</v>
+        <v>-1.46</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-120.79</t>
+          <t>-119.83</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>16885080</v>
+        <v>16454326</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>16004593.7</t>
+          <t>15267232.3</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>36758773.74</v>
+        <v>35965380.56</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>880486</t>
+          <t>1187093</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-3344484.617075008</t>
+          <t>-3140682.379864275</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1518577.775248263</t>
+          <t>-2019770.07520524</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>33968367.0</t>
+          <t>9653731.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>52.6</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>54.3</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>243.53</t>
+          <t>637.704</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.87</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,17 +5954,17 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5973,47 +5973,47 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.27</v>
+        <v>0.46</v>
       </c>
       <c r="AU12" t="n">
-        <v>-2.07</v>
+        <v>-1.42</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-6.13</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>52.56</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>53.55</v>
+        <v>53.32</v>
       </c>
       <c r="AZ12" t="n">
-        <v>57.04</v>
+        <v>56.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>58.23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.43</v>
+        <v>-1.31</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.59</v>
+        <v>-1.53</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-121.53</t>
+          <t>-120.79</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>325914545.495671</t>
+          <t>325464062.0036023</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>12528723.8</v>
+        <v>16885080</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>13748644.2</t>
+          <t>16004593.7</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>37439432.96</v>
+        <v>36758773.74</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-1219920</t>
+          <t>880486</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-3676467.679225326</t>
+          <t>-3344484.617075008</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3353493.426193714</t>
+          <t>-1518577.775248263</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>12796449.0</t>
+          <t>33968367.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>16.57</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>27.83</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/影像遙測.xlsx
+++ b/Result/checksun_type/影像遙測.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV12"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -933,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>169.583</t>
+          <t>167.285</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.26</t>
+          <t>-18.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,300 +1118,305 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-04-24 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
           <t>0.21</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
-      </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.99</v>
+          <t>23.08</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>14.36</t>
+        </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-4.78</t>
-        </is>
+        <v>-0.15</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.06</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>52.72000000000001</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>52.55</v>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>52.58000000000001</t>
+        </is>
       </c>
       <c r="AZ2" t="n">
-        <v>55.19</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>57.54</t>
-        </is>
+        <v>52.61</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>55.02</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>21.59</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.64</v>
+          <t>57.42</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>20.73</t>
+        </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+        <v>-0.61</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-111.02</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
+          <t>-110.47</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>325464062.0036023</t>
-        </is>
-      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>8852668.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10392277</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>12870889.2</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>28000317.22</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-2478612</t>
-        </is>
+          <t>325014702.1985612</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>8772665.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>10372623.4</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>12782782.6</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>27622061.74</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-2000396.286373935</t>
+          <t>-2410159</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1742398.498316802</t>
+          <t>-1972626.907514392</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>8852668.0</t>
+          <t>-1819895.323786909</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8772665.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-10.62</t>
-        </is>
-      </c>
       <c r="BU2" t="inlineStr">
         <is>
+          <t>-10.10</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
       <c r="CI2" t="inlineStr">
         <is>
+          <t>16.51</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
+          <t>5250</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>52.3</t>
-        </is>
-      </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>52.2</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1425,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>265.598</t>
+          <t>169.583</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1460,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1470,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.96</t>
+          <t>-19.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,300 +1605,305 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-04-24 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>26.11</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>-0.3</v>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>-5.09</t>
-        </is>
+        <v>-0.99</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.32</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>52.86</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>52.56</v>
+          <t>-4.08</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>52.72000000000001</t>
+        </is>
       </c>
       <c r="AZ3" t="n">
-        <v>55.38</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>57.61</t>
-        </is>
+        <v>52.55</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>55.19</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>26.57</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.63</v>
+          <t>57.54</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>21.59</t>
+        </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+        <v>-0.64</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-111.61</t>
-        </is>
-      </c>
       <c r="BG3" t="inlineStr">
         <is>
+          <t>-111.02</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>325464062.0036023</t>
-        </is>
-      </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>14156741.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>11234589</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>15382459.1</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
-        <v>28922957.26</v>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-4147870</t>
-        </is>
+          <t>325014702.1985612</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>8852668.0</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>10392277</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>12870889.2</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>28000317.22</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-2047304.975111595</t>
+          <t>-2478612</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1578031.979848191</t>
+          <t>-2000396.286373935</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>14156741.0</t>
+          <t>-1742398.498316802</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8852668.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-9.76</t>
-        </is>
-      </c>
       <c r="BU3" t="inlineStr">
         <is>
+          <t>-10.62</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
       <c r="CI3" t="inlineStr">
         <is>
+          <t>16.51</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
+          <t>5250</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
         <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
+          <t>52.2</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1907,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>252.353</t>
+          <t>265.598</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,437 +1937,437 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-26.96</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-14.31</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/05/26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>59.1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/05/27</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>59.3</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/11/07</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/22</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2025-04-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>26.11</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>-5.09</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>-3.87</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>52.86</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>57.61</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>26.57</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-111.61</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>325014702.1985612</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>14156741.0</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>11234589</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>15382459.1</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
+        <v>28922957.26</v>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-4147870</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-2047304.975111595</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-1578031.979848191</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>14156741.0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>-9.76</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>16.51</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>27.88</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>5250</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
           <t>52.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-15.65</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-14.63</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/05/26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>59.1</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>57.9</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/05/27</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>59.3</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/11/07</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/09/22</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>44.44</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>-5.44</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>-3.71</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>53.02</t>
-        </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>52.52</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>57.68</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>27.72</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>7.38</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-112.38</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>325464062.0036023</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>13183402.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12860748</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>15246429.9</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>29156371.74</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-2385681</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-2132627.33788676</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-1855157.918469884</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>13183402.0</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>-10.10</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>凌群</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>-13.01541036036408</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>5.576499396182672</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>7.68516930639722</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>18.50</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>25.81%</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>3.37%</t>
-        </is>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>凌群-資訊服務業-上市</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
-        <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -2362,15 +2377,20 @@
       </c>
       <c r="CT4" t="inlineStr">
         <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2389,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>129.578</t>
+          <t>252.353</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2444,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-15.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.82</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,300 +2579,305 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-04-24 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>61.11</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>-0.3</v>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>44.44</t>
+        </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>-5.76</t>
-        </is>
+        <v>-0.98</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.96</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>53.16</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>52.48</v>
+          <t>-3.71</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>53.02</t>
+        </is>
       </c>
       <c r="AZ5" t="n">
-        <v>55.69</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>57.74</t>
-        </is>
+        <v>52.52</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>55.54</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>31.38</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-0.67</v>
+          <t>57.68</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>27.72</t>
+        </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="BE5" t="inlineStr">
+        <v>-0.66</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="BF5" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>-113.24</t>
-        </is>
-      </c>
       <c r="BG5" t="inlineStr">
         <is>
+          <t>-112.38</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>2025/12/01</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>325464062.0036023</t>
-        </is>
-      </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>6897641.0</t>
-        </is>
-      </c>
-      <c r="BJ5" t="n">
-        <v>14493492.4</v>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>15085603.2</t>
-        </is>
-      </c>
-      <c r="BL5" t="n">
-        <v>31088486.92</v>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-592110</t>
-        </is>
+          <t>325014702.1985612</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>13183402.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>12860748</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>15246429.9</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>29156371.74</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-2183076.323235282</t>
+          <t>-2385681</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2080510.155126946</t>
+          <t>-2132627.33788676</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>6897641.0</t>
+          <t>-1855157.918469884</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13183402.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>-9.25</t>
-        </is>
-      </c>
       <c r="BU5" t="inlineStr">
         <is>
+          <t>-10.10</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-13.01541036036408</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>5.576499396182672</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>7.68516930639722</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>4.95</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
       <c r="CI5" t="inlineStr">
         <is>
+          <t>16.51</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>27.51</t>
-        </i